--- a/output/rup/2026/Rekap RUP Tahun 2026 (2026-06-15) Legacy.xlsx
+++ b/output/rup/2026/Rekap RUP Tahun 2026 (2026-06-15) Legacy.xlsx
@@ -869,19 +869,19 @@
         <v>2474291200</v>
       </c>
       <c r="D15" s="3" t="n">
-        <v>2474291200</v>
+        <v>2604091200</v>
       </c>
       <c r="E15" s="3" t="n">
         <v>0</v>
       </c>
       <c r="F15" s="3" t="n">
-        <v>2474291200</v>
+        <v>2604091200</v>
       </c>
       <c r="G15" s="3" t="n">
-        <v>0</v>
+        <v>129800000</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>100</v>
+        <v>105.2459467988246</v>
       </c>
     </row>
     <row r="16">

--- a/output/rup/2026/Rekap RUP Tahun 2026 (2026-06-15) Legacy.xlsx
+++ b/output/rup/2026/Rekap RUP Tahun 2026 (2026-06-15) Legacy.xlsx
@@ -869,19 +869,19 @@
         <v>2474291200</v>
       </c>
       <c r="D15" s="3" t="n">
-        <v>2604091200</v>
+        <v>2474291200</v>
       </c>
       <c r="E15" s="3" t="n">
         <v>0</v>
       </c>
       <c r="F15" s="3" t="n">
-        <v>2604091200</v>
+        <v>2474291200</v>
       </c>
       <c r="G15" s="3" t="n">
-        <v>129800000</v>
+        <v>0</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>105.2459467988246</v>
+        <v>100</v>
       </c>
     </row>
     <row r="16">
@@ -1233,19 +1233,19 @@
         <v>1858317230</v>
       </c>
       <c r="D28" s="3" t="n">
-        <v>1858317230</v>
+        <v>1975294025</v>
       </c>
       <c r="E28" s="3" t="n">
         <v>0</v>
       </c>
       <c r="F28" s="3" t="n">
-        <v>1858317230</v>
+        <v>1975294025</v>
       </c>
       <c r="G28" s="3" t="n">
-        <v>0</v>
+        <v>116976795</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>100</v>
+        <v>106.2947699731547</v>
       </c>
     </row>
     <row r="29">

--- a/output/rup/2026/Rekap RUP Tahun 2026 (2026-06-15) Legacy.xlsx
+++ b/output/rup/2026/Rekap RUP Tahun 2026 (2026-06-15) Legacy.xlsx
@@ -981,19 +981,19 @@
         <v>2181147677</v>
       </c>
       <c r="D19" s="3" t="n">
-        <v>2181147677</v>
+        <v>2181861827</v>
       </c>
       <c r="E19" s="3" t="n">
         <v>0</v>
       </c>
       <c r="F19" s="3" t="n">
-        <v>2181147677</v>
+        <v>2181861827</v>
       </c>
       <c r="G19" s="3" t="n">
-        <v>0</v>
+        <v>714150</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>100</v>
+        <v>100.0327419370789</v>
       </c>
     </row>
     <row r="20">

--- a/output/rup/2026/Rekap RUP Tahun 2026 (2026-06-15) Legacy.xlsx
+++ b/output/rup/2026/Rekap RUP Tahun 2026 (2026-06-15) Legacy.xlsx
@@ -869,19 +869,19 @@
         <v>2474291200</v>
       </c>
       <c r="D15" s="3" t="n">
-        <v>2474291200</v>
+        <v>2604091200</v>
       </c>
       <c r="E15" s="3" t="n">
         <v>0</v>
       </c>
       <c r="F15" s="3" t="n">
-        <v>2474291200</v>
+        <v>2604091200</v>
       </c>
       <c r="G15" s="3" t="n">
-        <v>0</v>
+        <v>129800000</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>100</v>
+        <v>105.2459467988246</v>
       </c>
     </row>
     <row r="16">
@@ -981,19 +981,19 @@
         <v>2181147677</v>
       </c>
       <c r="D19" s="3" t="n">
-        <v>2181861827</v>
+        <v>2181147677</v>
       </c>
       <c r="E19" s="3" t="n">
         <v>0</v>
       </c>
       <c r="F19" s="3" t="n">
-        <v>2181861827</v>
+        <v>2181147677</v>
       </c>
       <c r="G19" s="3" t="n">
-        <v>714150</v>
+        <v>0</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>100.0327419370789</v>
+        <v>100</v>
       </c>
     </row>
     <row r="20">
@@ -1233,19 +1233,19 @@
         <v>1858317230</v>
       </c>
       <c r="D28" s="3" t="n">
-        <v>1975294025</v>
+        <v>1858317230</v>
       </c>
       <c r="E28" s="3" t="n">
         <v>0</v>
       </c>
       <c r="F28" s="3" t="n">
-        <v>1975294025</v>
+        <v>1858317230</v>
       </c>
       <c r="G28" s="3" t="n">
-        <v>116976795</v>
+        <v>0</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>106.2947699731547</v>
+        <v>100</v>
       </c>
     </row>
     <row r="29">

--- a/output/rup/2026/Rekap RUP Tahun 2026 (2026-06-15) Legacy.xlsx
+++ b/output/rup/2026/Rekap RUP Tahun 2026 (2026-06-15) Legacy.xlsx
@@ -869,19 +869,19 @@
         <v>2474291200</v>
       </c>
       <c r="D15" s="3" t="n">
-        <v>2604091200</v>
+        <v>2474291200</v>
       </c>
       <c r="E15" s="3" t="n">
         <v>0</v>
       </c>
       <c r="F15" s="3" t="n">
-        <v>2604091200</v>
+        <v>2474291200</v>
       </c>
       <c r="G15" s="3" t="n">
-        <v>129800000</v>
+        <v>0</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>105.2459467988246</v>
+        <v>100</v>
       </c>
     </row>
     <row r="16">
